--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y21</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y20"/>
+  <dimension ref="A1:Y21"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -1969,10 +1969,87 @@
         <v>2026-08-05T15:35:00Z</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>DF-00020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-08-05T20:38:32.000Z</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Fw: [Spam] eakstone Opportunity - Motorization Solutions for High Growth Interior Shading &amp; Outdoor Living Markets ($4.6 million EBITDA).</v>
+      </c>
+      <c r="D21" t="str">
+        <v>joe@xipllc.com (fwd from dealdesk@peakzone.com)</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Bank</v>
+      </c>
+      <c r="F21" t="str">
+        <v>APEX (project codename; motorization/controls manufacturer)</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Consumer products/brand (smart motorization hardware for interior shading &amp; outdoor living)</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Australia, New Zealand, North America</v>
+      </c>
+      <c r="I21" t="str">
+        <v>$4.6M (Adjusted, 2026 projected)</v>
+      </c>
+      <c r="J21" t="str">
+        <v>$12.5M (2026 projected)</v>
+      </c>
+      <c r="K21" t="str">
+        <v>~36.8% (calculated from projected figures)</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M21" t="str">
+        <v>Asset-light, high-margin distribution model; exclusive distribution rights across four regions; lean regional infrastructure</v>
+      </c>
+      <c r="N21" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="O21" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P21" t="str">
+        <v>Peakstone Group (sell-side advisor)</v>
+      </c>
+      <c r="Q21" t="str">
+        <v>NDA and Executive Summary linked in email, to be returned to APEX@peakstone.com to advance. CAUTION: sender domain (dealdesk@peakzone.com) does not match the advisor's stated name/links (Peakstone / peakstonegroup.com) and Outlook auto-tagged the original as [Spam] -- possible lookalike-domain/phishing indicator, verify advisor identity before engaging.</v>
+      </c>
+      <c r="R21">
+        <v>49</v>
+      </c>
+      <c r="S21" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T21" t="str">
+        <v>Hard-disqualified: APEX is a technology-enabled manufacturer/distributor of motorization hardware (motors, controls) for interior shading and outdoor living products sold through B2B dealers -- a consumer product/hardware brand with no infrastructure asset-operating character, not a residential service business, so it scores 0 on End-Market Fit and auto-tiers Pass despite an attractive $4.6M EBITDA / ~37% margin profile.</v>
+      </c>
+      <c r="U21" t="str">
+        <v>N</v>
+      </c>
+      <c r="V21" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAADY4K7pAAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W21" t="str">
+        <v>New</v>
+      </c>
+      <c r="X21" t="str">
+        <v>&lt;DM6PR13MB4348BCBEFB98BEEF8996EA75D7D32@DM6PR13MB4348.namprd13.prod.outlook.com&gt;</v>
+      </c>
+      <c r="Y21" t="str">
+        <v>2026-08-05T20:45:00.000Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y20"/>
+  <autoFilter ref="A1:Y21"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y21"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y22</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y21"/>
+  <dimension ref="A1:Y22"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -2046,10 +2046,87 @@
         <v>2026-08-05T20:45:00.000Z</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>DF-00021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-08-14T16:02:26.000Z</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Deal Flow Friday: Active Sell-Side Engagements</v>
+      </c>
+      <c r="D22" t="str">
+        <v>dealflow@mariner.com</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Unknown (blind teaser: "Construction &amp; Engineering" business, CAD $11.1M EBITDA)</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Energy Infrastructure Services</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Unknown (EBITDA stated in CAD, suggesting Canada, but not explicitly stated)</v>
+      </c>
+      <c r="I22" t="str">
+        <v>CAD $11.1M</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M22" t="str">
+        <v>Construction &amp; Engineering (capex-heavy)</v>
+      </c>
+      <c r="N22" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="O22" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P22" t="str">
+        <v>Mariner (Woodbridge International LLC, a subsidiary of Mariner Wealth Advisors)</v>
+      </c>
+      <c r="Q22" t="str">
+        <v>Blind teaser (no company name) from Mariner's weekly "Deal Flow Friday" advertisement/marketing digest email; only an NDA link was provided, not accessed. Email bundled 25 other one-line teasers across mixed sectors (consumer product brands, professional/consulting services, manufacturing, generic trade contracting, environmental remediation, IT managed services, etc.); all were excluded as either out of mandate (consumer brands, professional services, manufacturing) or too generic/unconfirmed to confidently place as core infrastructure (electrical/environmental/valve "services" teasers with no stated utility, grid, or infra-asset context). This was the only line item with an explicit "Energy Infrastructure Services" sector tag.</v>
+      </c>
+      <c r="R22">
+        <v>67</v>
+      </c>
+      <c r="S22" t="str">
+        <v>Fit</v>
+      </c>
+      <c r="T22" t="str">
+        <v>Explicitly tagged "Energy Infrastructure Services" end-market (35/35) and mid-size EBITDA in the sweet-spot range (24/30, margin unstated) place this in the Fit tier, but it's a fully blind, unnamed teaser with capex-heavy business model and no management/systems detail, so treat as low-confidence until a company name and NDA-stage detail are available.</v>
+      </c>
+      <c r="U22" t="str">
+        <v>N</v>
+      </c>
+      <c r="V22" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAADvGMdQAAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W22" t="str">
+        <v>New</v>
+      </c>
+      <c r="X22" t="str">
+        <v>&lt;1142338896180.1142301062071.1067269665.0.1391200JL.2002@synd.ccsend.com&gt;</v>
+      </c>
+      <c r="Y22" t="str">
+        <v>2026-08-14T17:00:26Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y21"/>
+  <autoFilter ref="A1:Y22"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y22"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y23</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y22"/>
+  <dimension ref="A1:Y23"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -2123,10 +2123,87 @@
         <v>2026-08-14T17:00:26Z</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>DF-00022</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-08-17T13:15:01.000Z</v>
+      </c>
+      <c r="C23" t="str">
+        <v>New Listing: Greater Boston Liquor Store in Affluent Boston Suburb</v>
+      </c>
+      <c r="D23" t="str">
+        <v>admin@baystatebusinessbrokers.com</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Unknown (blind listing: "Greater Boston Liquor Store", Listing #1927 -- name/address withheld pre-NDA)</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Consumer products/brand (off-premise retail liquor/package store -- no infrastructure asset-operating character)</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Greater Boston, MA (affluent suburb; specific town withheld pre-NDA)</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Unknown (2025 SDE stated as $131,833, not EBITDA)</v>
+      </c>
+      <c r="J23" t="str">
+        <v>$2,072,371 (2025)</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="L23" t="str">
+        <v>$1,100,000 + Inventory</v>
+      </c>
+      <c r="M23" t="str">
+        <v>Retail (off-premise alcohol package store); not O&amp;M/infra-service oriented</v>
+      </c>
+      <c r="N23" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="O23" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P23" t="str">
+        <v>BayState Business Brokers (Brian Labonte)</v>
+      </c>
+      <c r="Q23" t="str">
+        <v>Broker mass 'New Listing' blast (Listing 1927); requires clicking to sign an NDA/Confidentiality Agreement before target name/address is released. No attachments.</v>
+      </c>
+      <c r="R23">
+        <v>12</v>
+      </c>
+      <c r="S23" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T23" t="str">
+        <v>A single-location off-premise liquor/package retail store is a consumer product/retail business with no infrastructure asset-operating character, so it hard-disqualifies on End-Market Fit (0/35) and auto-tiers Pass despite a modest asking price and clean license/lease terms.</v>
+      </c>
+      <c r="U23" t="str">
+        <v>N</v>
+      </c>
+      <c r="V23" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAD02HDEAAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W23" t="str">
+        <v>New</v>
+      </c>
+      <c r="X23" t="str">
+        <v>&lt;0c54b703-cc38-561f-a1a9-6b9d5f3f18d1@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y23" t="str">
+        <v>2026-08-17T13:49:57Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y22"/>
+  <autoFilter ref="A1:Y23"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y23"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y24</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y23"/>
+  <dimension ref="A1:Y24"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -2200,10 +2200,87 @@
         <v>2026-08-17T13:49:57Z</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>DF-00023</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-08-17T22:37:45.000Z</v>
+      </c>
+      <c r="C24" t="str">
+        <v>EARLY ACCESS: New Listing 1928: Multi-Residential Plumbing &amp; HVAC Contractor Service MA</v>
+      </c>
+      <c r="D24" t="str">
+        <v>admin@baystatebusinessbrokers.com</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Unknown (blind listing: "Multi-Residential Plumbing and HVAC Contractor Service MA", Listing #1928 -- name/address withheld pre-NDA)</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Consumer-facing business within mandate (residential/multi-residential plumbing &amp; HVAC contractor service; property-manager-facing home-services model, not a consumer product/brand)</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Massachusetts (statewide; specific location withheld pre-NDA)</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Unknown (2025 SDE stated as $1,533,584, not EBITDA)</v>
+      </c>
+      <c r="J24" t="str">
+        <v>$5,093,427 (2025); 2026 sales on track to exceed $5.5M</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="L24" t="str">
+        <v>$5,100,000 (Business Price)</v>
+      </c>
+      <c r="M24" t="str">
+        <v>Service/O&amp;M-oriented (plumbing &amp; HVAC repair, routine and emergency maintenance, 24-hour emergency service, high-margin replacements) for multi-residential property managers</v>
+      </c>
+      <c r="N24" t="str">
+        <v>Semi-absentee ownership (~10% and 5% of time actively in the business); no stated ERP/systems or professional CEO/CFO</v>
+      </c>
+      <c r="O24" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P24" t="str">
+        <v>BayState Business Brokers (Brian Labonte)</v>
+      </c>
+      <c r="Q24" t="str">
+        <v>Broker mass 'EARLY ACCESS' blast (Listing 1928), available to 'Preferred Buyers' for one week; requires signup/NDA before target name/address released. No attachments.</v>
+      </c>
+      <c r="R24">
+        <v>40</v>
+      </c>
+      <c r="S24" t="str">
+        <v>Marginal</v>
+      </c>
+      <c r="T24" t="str">
+        <v>A multi-residential plumbing &amp; HVAC service business is a consumer/property-facing service company that is in-mandate but downweighted on End-Market Fit, and scores modestly overall given sub-$3M reported earnings (SDE, not EBITDA), semi-absentee ownership with no stated management systems, and broker-sourced deal flow, landing it in the Marginal tier.</v>
+      </c>
+      <c r="U24" t="str">
+        <v>N</v>
+      </c>
+      <c r="V24" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAD02HDFAAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W24" t="str">
+        <v>New</v>
+      </c>
+      <c r="X24" t="str">
+        <v>&lt;269bba4e-bac5-5782-a070-a0de41b5df58@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y24" t="str">
+        <v>2026-08-17T22:50:01Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y23"/>
+  <autoFilter ref="A1:Y24"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y24"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y25</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:Y25"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -2277,10 +2277,87 @@
         <v>2026-08-17T22:50:01Z</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>DF-00024</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2026-08-21T16:03:48.000Z</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Deal Flow Friday: Active Sell-Side Engagements</v>
+      </c>
+      <c r="D25" t="str">
+        <v>dealflow@mariner.com</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Unknown (blind teaser: "Construction &amp; Engineering" business, CAD $11.1M EBITDA)</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Energy Infrastructure Services</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Unknown (EBITDA stated in CAD, suggesting Canada, but not explicitly stated)</v>
+      </c>
+      <c r="I25" t="str">
+        <v>CAD $11.1M</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M25" t="str">
+        <v>Construction &amp; Engineering (capex-heavy)</v>
+      </c>
+      <c r="N25" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="O25" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P25" t="str">
+        <v>Mariner (Woodbridge International LLC, a subsidiary of Mariner Wealth Advisors)</v>
+      </c>
+      <c r="Q25" t="str">
+        <v>Blind teaser (no company name) from Mariner's weekly "Deal Flow Friday" advertisement/marketing digest; only an NDA link provided, not accessed. This 2026-08-21 blast is a re-appearance of the same "Energy Infrastructure Services / Construction &amp; Engineering, CAD $11.1M EBITDA" line already captured as DF-00021 (2026-08-14). Logged separately because it arrived during a routine outage (no runs 2026-08-19 16:00Z through 2026-08-22 21:49Z) and was only scanned now; distinct messageId so not auto-deduped. Email bundled ~26 other one-line teasers across mixed sectors (aerospace/defense, consumer product brands, professional/consulting services, manufacturing, generic trade contracting, environmental remediation, IT managed services, etc.); all excluded as out of mandate or too generic/unconfirmed to place as core infrastructure. This was the only line item with an explicit "Energy Infrastructure Services" sector tag.</v>
+      </c>
+      <c r="R25">
+        <v>67</v>
+      </c>
+      <c r="S25" t="str">
+        <v>Fit</v>
+      </c>
+      <c r="T25" t="str">
+        <v>Explicitly tagged "Energy Infrastructure Services" end-market (35/35) with mid-size EBITDA in the sweet-spot range (24/30, margin unstated) places it in the Fit tier, but it is a fully blind, unnamed, capex-heavy teaser that repeats DF-00021 with no new detail, so treat as low-confidence until a company name and NDA-stage detail emerge.</v>
+      </c>
+      <c r="U25" t="str">
+        <v>N</v>
+      </c>
+      <c r="V25" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAD9w2CcAAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W25" t="str">
+        <v>New</v>
+      </c>
+      <c r="X25" t="str">
+        <v>&lt;1142340277924.1142301062071.1067269665.0.1431200JL.2002@synd.ccsend.com&gt;</v>
+      </c>
+      <c r="Y25" t="str">
+        <v>2026-08-24T02:50:00Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y24"/>
+  <autoFilter ref="A1:Y25"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y25"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y26</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y25"/>
+  <dimension ref="A1:Y26"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -2354,10 +2354,87 @@
         <v>2026-08-24T02:50:00Z</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>DF-00025</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2026-08-24T15:17:12.000Z</v>
+      </c>
+      <c r="C26" t="str">
+        <v>New Listing: 1928, Multi-Residential Plumbing &amp; HVAC Contractor Serving Massachusetts</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Baystate Business Brokers &lt;admin@baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Multi-Residential Plumbing &amp; HVAC Contractor (BayState Listing 1928) - company name withheld pending NDA</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Other Infra (building-systems service - plumbing/HVAC)</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Massachusetts</v>
+      </c>
+      <c r="I26" t="str">
+        <v>$1,533,584 (stated as 2025 SDE, not EBITDA)</v>
+      </c>
+      <c r="J26" t="str">
+        <v>$5,093,427 (2025); on track to exceed $5.5M in 2026</v>
+      </c>
+      <c r="K26" t="str">
+        <v>~30% (SDE/Revenue, not a true EBITDA margin)</v>
+      </c>
+      <c r="L26" t="str">
+        <v>$5,100,000</v>
+      </c>
+      <c r="M26" t="str">
+        <v>Service/O&amp;M - plumbing &amp; HVAC repair, maintenance, and replacements for multi-residential (property manager) customers; 24-hour emergency service</v>
+      </c>
+      <c r="N26" t="str">
+        <v>Unknown - semi-absentee ownership (owners spend ~10% and ~5% of time in the business), no CEO/CFO or ERP system stated</v>
+      </c>
+      <c r="O26" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P26" t="str">
+        <v>BayState Business Brokers</v>
+      </c>
+      <c r="Q26" t="str">
+        <v>Marketing-style broker listing (no attachment); NDA sign-link provided to access full CIM/company name, not accessed. Semi-absentee ownership cited as transition opportunity with limited owner dependence. Same broker as prior DF-00023 (BayState plumbing/HVAC contractor, Marginal).</v>
+      </c>
+      <c r="R26">
+        <v>49</v>
+      </c>
+      <c r="S26" t="str">
+        <v>Marginal</v>
+      </c>
+      <c r="T26" t="str">
+        <v>Sub-scale ($1.5M SDE, below the $3M EBITDA sweet-spot floor) service business tied to building plumbing/HVAC systems rather than a core energy/telecom/water/transportation asset, with unconfirmed management depth, lands in the Marginal tier.</v>
+      </c>
+      <c r="U26" t="str">
+        <v>N</v>
+      </c>
+      <c r="V26" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAEEiMJ7AAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W26" t="str">
+        <v>New</v>
+      </c>
+      <c r="X26" t="str">
+        <v>&lt;e36f9383-a804-54c9-9467-f57045830f23@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y26" t="str">
+        <v>2026-08-24T15:30:00Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y25"/>
+  <autoFilter ref="A1:Y26"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y26"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y27</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Y27"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -2431,10 +2431,87 @@
         <v>2026-08-24T15:30:00Z</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>DF-00026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2026-08-27T17:26:55.000Z</v>
+      </c>
+      <c r="C27" t="str">
+        <v>EARLY ACCESS: New Listing 1931: Recurring Revenue Boiler and Water Heater Rental Business</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Baystate Business Brokers &lt;admin@baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Recurring Revenue Boiler &amp; Water Heater Rental Business (BayState Listing 1931) - company name withheld pending NDA</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Consumer-Facing Home Energy Services (boiler &amp; water heater rental, within mandate)</v>
+      </c>
+      <c r="H27" t="str">
+        <v>New England</v>
+      </c>
+      <c r="I27" t="str">
+        <v>$460,956 (stated as 2026 SDE through June, annualized, not EBITDA)</v>
+      </c>
+      <c r="J27" t="str">
+        <v>$1,663,991 (2026 through June, annualized)</v>
+      </c>
+      <c r="K27" t="str">
+        <v>~27.7% (SDE/Revenue, not a true EBITDA margin)</v>
+      </c>
+      <c r="L27" t="str">
+        <v>$1,495,000</v>
+      </c>
+      <c r="M27" t="str">
+        <v>Rental + Service - recurring-revenue water heater &amp; boiler rentals on 5-yr auto-renewing contracts (~75% of sales) plus rent-to-own boiler/water-heater agreements and supplemental rentals (~25% of sales), with ongoing service; ~97% of customers under rental arrangements</v>
+      </c>
+      <c r="N27" t="str">
+        <v>Partial - semi-absentee ownership; day-to-day office functions managed by an Operations Supervisor, owner spends ~15 hrs/week on major approvals; no CEO/CFO or ERP system stated</v>
+      </c>
+      <c r="O27" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P27" t="str">
+        <v>BayState Business Brokers</v>
+      </c>
+      <c r="Q27" t="str">
+        <v>Marketing-style broker 'Early Access' listing (no attachment); no NDA/CIM accessed, listing stated as available to Preferred Buyers for one week only. Semi-absentee day-to-day operations (Operations Supervisor-run) cited as transition opportunity. Same broker as prior DF-00023/DF-00025 (BayState plumbing/HVAC contractor listings).</v>
+      </c>
+      <c r="R27">
+        <v>44</v>
+      </c>
+      <c r="S27" t="str">
+        <v>Marginal</v>
+      </c>
+      <c r="T27" t="str">
+        <v>Sub-scale ($461K SDE, well below the $3M EBITDA sweet-spot floor) recurring-revenue home water heater/boiler rental business fits the consumer-facing home-energy-services niche within mandate, but small size and unconfirmed management depth land it in the Marginal tier.</v>
+      </c>
+      <c r="U27" t="str">
+        <v>N</v>
+      </c>
+      <c r="V27" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAELubddAAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W27" t="str">
+        <v>New</v>
+      </c>
+      <c r="X27" t="str">
+        <v>&lt;ea4f9b21-28d8-584e-b0c0-4d17b88c4508@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y27" t="str">
+        <v>2026-08-27T17:49:33Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y26"/>
+  <autoFilter ref="A1:Y27"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y27"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y28</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y27"/>
+  <dimension ref="A1:Y28"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -2508,10 +2508,87 @@
         <v>2026-08-27T17:49:33Z</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>DF-00027</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2026-08-27T20:44:54.000Z</v>
+      </c>
+      <c r="C28" t="str">
+        <v>EARLY ACCESS: New Listing 1926, Food Service Business with Strong Retail Demand and Wholesale Growth Potential</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Baystate Business Brokers &lt;admin@baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Unknown (blind listing: "Food Service Business", Listing #1926 -- name/address withheld pre-NDA)</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Consumer products/brand (food service/bakery retail &amp; takeout -- no infrastructure asset-operating character)</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Greater Boston, MA</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Unknown (2025 SDE stated as $994,819, not EBITDA)</v>
+      </c>
+      <c r="J28" t="str">
+        <v>$2,662,778 (2025)</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Offers Accepted (no headline price stated)</v>
+      </c>
+      <c r="M28" t="str">
+        <v>Retail food service/takeout with wholesale bread production upside; not O&amp;M/infra-service oriented</v>
+      </c>
+      <c r="N28" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="O28" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P28" t="str">
+        <v>BayState Business Brokers (Bil Zarch)</v>
+      </c>
+      <c r="Q28" t="str">
+        <v>Broker 'Early Access' marketing blast (Listing 1926); listing stated as available to Preferred Buyers for one week only. No attachments, no NDA/CIM accessed. Same broker as prior DF-00022/00023/00025/00026 (BayState) listings.</v>
+      </c>
+      <c r="R28">
+        <v>15</v>
+      </c>
+      <c r="S28" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T28" t="str">
+        <v>A takeout/delivery food-service and wholesale-bread retail business is a consumer product/retail business with no infrastructure asset-operating character, so it hard-disqualifies on End-Market Fit (0/35) and auto-tiers Pass despite sub-$3M SDE and an unset asking price.</v>
+      </c>
+      <c r="U28" t="str">
+        <v>N</v>
+      </c>
+      <c r="V28" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAELubdeAAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W28" t="str">
+        <v>New</v>
+      </c>
+      <c r="X28" t="str">
+        <v>&lt;51107fb3-a832-58c2-8afb-ca311b94ec73@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y28" t="str">
+        <v>2026-08-27T20:49:56Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y27"/>
+  <autoFilter ref="A1:Y28"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y28"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y29</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y28"/>
+  <dimension ref="A1:Y29"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -2585,10 +2585,87 @@
         <v>2026-08-27T20:49:56Z</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>DF-00028</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2026-08-28</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Listing: 1838, Tax Preparation &amp; Accounting Services with Updated Financials &amp; Asking Price</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Baystate Business Brokers &lt;admin@baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Unknown (anonymized broker listing 1838 - Tax Prep &amp; Accounting firm)</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Professional services (tax preparation, bookkeeping &amp; accounting) - not infrastructure, out of mandate</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Middlesex County, MA</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Unknown (SDE stated instead: $149,208 TTM as of 7/31/2026)</v>
+      </c>
+      <c r="J29" t="str">
+        <v>$931,442 (TTM as of 7/31/2026)</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Unknown (SDE margin ~16% of revenue, not a true EBITDA margin)</v>
+      </c>
+      <c r="L29" t="str">
+        <v>$549,000</v>
+      </c>
+      <c r="M29" t="str">
+        <v>Service (tax prep, bookkeeping, payroll, accounting)</v>
+      </c>
+      <c r="N29" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="O29" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P29" t="str">
+        <v>BayState Business Brokers</v>
+      </c>
+      <c r="Q29" t="str">
+        <v>Anonymized teaser listing, no attachment/CIM; NDA sign-link provided to unlock further detail; broker contact Phil Masotta.</v>
+      </c>
+      <c r="R29">
+        <v>30</v>
+      </c>
+      <c r="S29" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T29" t="str">
+        <v>Small family-style tax prep/accounting practice with no infrastructure or asset-operating character and sub-scale earnings ($149K SDE), well outside XIP's infra mandate.</v>
+      </c>
+      <c r="U29" t="str">
+        <v>N</v>
+      </c>
+      <c r="V29" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAEO8z08AAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W29" t="str">
+        <v>New</v>
+      </c>
+      <c r="X29" t="str">
+        <v>&lt;9cb434b8-96bf-5de5-84f1-4611361770d5@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y29" t="str">
+        <v>2026-08-28T21:49:58Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y28"/>
+  <autoFilter ref="A1:Y29"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y29"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y30</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y29"/>
+  <dimension ref="A1:Y30"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -2662,10 +2662,87 @@
         <v>2026-08-28T21:49:58Z</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>DF-00029</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2026-09-01T20:17:16Z</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Listing 1911: Established Southern New England Seafood and Meat Market with Real Estate</v>
+      </c>
+      <c r="D30" t="str">
+        <v>admin@baystatebusinessbrokers.com</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Established Southern New England Seafood and Meat Market with Real Estate (Listing 1911)</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Consumer products/brand (specialty grocery/seafood-meat retail) - out of mandate</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Southern New England</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="J30" t="str">
+        <v>$3,304,427 (4-year average)</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Unknown (SDE 4-yr avg $137,095, not EBITDA)</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Business: $399,000 + Inventory; Real Estate: $1,899,000</v>
+      </c>
+      <c r="M30" t="str">
+        <v>Retail specialty grocery (seafood/meat market with broadline groceries, deli, prepared foods)</v>
+      </c>
+      <c r="N30" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="O30" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P30" t="str">
+        <v>BayState Business Brokers</v>
+      </c>
+      <c r="Q30" t="str">
+        <v>NDA required via broker link before further info; real estate owned by sellers and all offers must include real estate; no attachments in email.</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T30" t="str">
+        <v>A regional specialty seafood/meat retail market is a consumer products/retail brand with no infrastructure or asset-operating character, so it is hard-disqualified per the rubric's consumer distinction regardless of its stable financials.</v>
+      </c>
+      <c r="U30" t="str">
+        <v>N</v>
+      </c>
+      <c r="V30" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAEVF7u7AAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W30" t="str">
+        <v>New</v>
+      </c>
+      <c r="X30" t="str">
+        <v>&lt;1167382b-a6e9-5bd4-ae61-0ceede64555b@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y30" t="str">
+        <v>2026-09-01T20:49:00Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y29"/>
+  <autoFilter ref="A1:Y30"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y30"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y31</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y30"/>
+  <dimension ref="A1:Y31"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -2739,10 +2739,87 @@
         <v>2026-09-01T20:49:00Z</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>DF-00030</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2026-09-02T15:57:05.000Z</v>
+      </c>
+      <c r="C31" t="str">
+        <v>New Listing 1926: Food Service Business with Strong Retail Demand &amp; Wholesale Growth Potential</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Baystate Business Brokers &lt;admin@baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Unknown (blind listing: "Food Service Business", Listing #1926 -- name/address withheld pre-NDA)</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Consumer products/brand (food service/bakery retail &amp; takeout -- no infrastructure asset-operating character)</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Greater Boston, MA</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Unknown (2025 SDE stated as $994,819, not EBITDA)</v>
+      </c>
+      <c r="J31" t="str">
+        <v>$2,662,778 (2025)</v>
+      </c>
+      <c r="K31" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Accepting Offers (no headline price stated)</v>
+      </c>
+      <c r="M31" t="str">
+        <v>Retail food service/takeout with wholesale bread production upside; not O&amp;M/infra-service oriented</v>
+      </c>
+      <c r="N31" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="O31" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P31" t="str">
+        <v>BayState Business Brokers (Bil Zarch)</v>
+      </c>
+      <c r="Q31" t="str">
+        <v>Re-send of Listing 1926 -- same underlying business, revenue, and SDE as DF-00027 (2026-08-27); this email uses the standard "New Listing" subject rather than the earlier "EARLY ACCESS" framing. No attachments, no NDA/CIM accessed. Same broker as prior DF-00022/00023/00025/00026/00027/00029 (BayState) listings.</v>
+      </c>
+      <c r="R31">
+        <v>15</v>
+      </c>
+      <c r="S31" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T31" t="str">
+        <v>A takeout/delivery food-service and wholesale-bread retail business is a consumer product/retail business with no infrastructure asset-operating character, so it hard-disqualifies on End-Market Fit (0/35) and auto-tiers Pass despite sub-$3M SDE and an unset asking price.</v>
+      </c>
+      <c r="U31" t="str">
+        <v>N</v>
+      </c>
+      <c r="V31" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAEVF7u9AAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W31" t="str">
+        <v>New</v>
+      </c>
+      <c r="X31" t="str">
+        <v>&lt;6dc9aeab-fbef-503d-aafe-233dff22aae2@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y31" t="str">
+        <v>2026-09-02T16:50:09Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y30"/>
+  <autoFilter ref="A1:Y31"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y31"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y32</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y31"/>
+  <dimension ref="A1:Y32"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -2816,10 +2816,87 @@
         <v>2026-09-02T16:50:09Z</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>DF-00031</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2026-09-03T15:31:52.000Z</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Listing: 1986, Profitable Tire and Auto Repair Business with Prime Real Estate</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Baystate Business Brokers &lt;admin@baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Unknown (anonymized broker listing 1986 - Tire &amp; Auto Repair business + real estate)</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Consumer products/brand (automotive tire &amp; repair retail service) - no infrastructure asset-operating character, out of mandate</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Unknown (not stated beyond "multiple contiguous markets")</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Unknown (SDE stated instead: $276,377 FYE June 2025)</v>
+      </c>
+      <c r="J32" t="str">
+        <v>$3,043,620 (FYE June 2025)</v>
+      </c>
+      <c r="K32" t="str">
+        <v>Unknown (SDE margin ~9.1% of revenue, not a true EBITDA margin)</v>
+      </c>
+      <c r="L32" t="str">
+        <v>$899,000 (Business) + $700,000 (Real Estate) = $1,599,000 bundled sale</v>
+      </c>
+      <c r="M32" t="str">
+        <v>Retail automotive tire sales &amp; repair services (oil changes, alignment, tire service) - consumer-facing service, not infra O&amp;M</v>
+      </c>
+      <c r="N32" t="str">
+        <v>Unknown (10 employees incl. ASE-certified techs, several with 5-40 yr tenure; no CEO/CFO or ERP system stated)</v>
+      </c>
+      <c r="O32" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P32" t="str">
+        <v>BayState Business Brokers (Ed Burkhart)</v>
+      </c>
+      <c r="Q32" t="str">
+        <v>Anonymized broker listing (Listing 1986), no attachment/CIM; NDA sign-link provided to unlock further detail; bundled sale requires purchase of owned real estate (17-space parking lot, appraised $1.4M); affiliated with Continental/General/Michelin tire brands.</v>
+      </c>
+      <c r="R32">
+        <v>20</v>
+      </c>
+      <c r="S32" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T32" t="str">
+        <v>A retail tire-and-auto-repair shop bundled with its real estate is a consumer service business with no infrastructure or asset-operating character, so it hard-disqualifies on End-Market Fit (0/35) and auto-tiers Pass despite modest, stable-looking revenue.</v>
+      </c>
+      <c r="U32" t="str">
+        <v>N</v>
+      </c>
+      <c r="V32" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAEVF7u%2FAAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W32" t="str">
+        <v>New</v>
+      </c>
+      <c r="X32" t="str">
+        <v>&lt;e05e4b82-e801-56ba-9b09-1477f1d70e58@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y32" t="str">
+        <v>2026-09-03T15:49:44Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y31"/>
+  <autoFilter ref="A1:Y32"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y32"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y33</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y32"/>
+  <dimension ref="A1:Y33"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -2893,10 +2893,87 @@
         <v>2026-09-03T15:49:44Z</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>DF-00032</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2026-09-04T16:05:52.000Z</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Deal Flow Friday: Active Sell-Side Engagements</v>
+      </c>
+      <c r="D33" t="str">
+        <v>dealflow@mariner.com</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Unknown (blind teaser: "Construction &amp; Engineering" business, CAD $11.1M EBITDA)</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Energy Infrastructure Services</v>
+      </c>
+      <c r="H33" t="str">
+        <v>Unknown (EBITDA stated in CAD, suggesting Canada, but not explicitly stated)</v>
+      </c>
+      <c r="I33" t="str">
+        <v>CAD $11.1M</v>
+      </c>
+      <c r="J33" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="K33" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M33" t="str">
+        <v>Construction &amp; Engineering (capex-heavy)</v>
+      </c>
+      <c r="N33" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="O33" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P33" t="str">
+        <v>Mariner (Woodbridge International LLC, a subsidiary of Mariner Wealth Advisors)</v>
+      </c>
+      <c r="Q33" t="str">
+        <v>Blind teaser (no company name) from Mariner's weekly "Deal Flow Friday" advertisement/marketing digest email; only an NDA link was provided, not accessed. Third appearance of this exact CAD $11.1M EBITDA / Energy Infrastructure Services line item, after DF-00021 (2026-08-14) and DF-00024 (2026-08-21); logged separately since it carries a distinct messageId, so not auto-deduped. Email bundled 24 other one-line teasers this run (food safety/FDA compliance consulting, grooming products brand, architecture/design services, military training/logistics, waste management, housing property manager, industrial components manufacturer, environmental remediation x2, real estate media, automotive parts manufacturer, IT infrastructure/managed services, cleaning/specialty chemicals, management consulting, IT/regulatory consulting, staffing, forest-products exporter, defense components procurement, valve services, aircraft parts/MRO); all excluded consistent with prior runs as either out of mandate (consumer brand, professional/consulting services, manufacturing, staffing, media, defense/aerospace, automotive) or too generic/unconfirmed to confidently place as core infrastructure (electrical/environmental/valve/IT-infra "services" teasers with no stated utility, grid, or infra-asset context). This was again the only line item with an explicit "Energy Infrastructure Services" sector tag.</v>
+      </c>
+      <c r="R33">
+        <v>67</v>
+      </c>
+      <c r="S33" t="str">
+        <v>Fit</v>
+      </c>
+      <c r="T33" t="str">
+        <v>Explicitly tagged "Energy Infrastructure Services" end-market (35/35) with mid-size EBITDA in the sweet-spot range (24/30, margin unstated) places it in the Fit tier, but it is a fully blind, unnamed, capex-heavy teaser repeating DF-00021/DF-00024 with no new detail, so treat as low-confidence until a company name and NDA-stage detail emerge.</v>
+      </c>
+      <c r="U33" t="str">
+        <v>N</v>
+      </c>
+      <c r="V33" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAEVF7vAAAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W33" t="str">
+        <v>New</v>
+      </c>
+      <c r="X33" t="str">
+        <v>&lt;1142343648623.1142301062071.1067269665.0.1361200JL.2002@synd.ccsend.com&gt;</v>
+      </c>
+      <c r="Y33" t="str">
+        <v>2026-09-04T16:15:00Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y32"/>
+  <autoFilter ref="A1:Y33"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y33"/>
   </ignoredErrors>
 </worksheet>
 </file>